--- a/Diagrama de Gantt.xlsx
+++ b/Diagrama de Gantt.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\df335\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\df335\Desktop\ProyectoFinDeCursoGrupo5\ProyectoFinDeCursoGrupo5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B91ED9EC-D1FD-4E10-AEA9-DA74398BE995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52517594-123F-4E85-90C9-16056C31DD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{75261B6F-E73A-4DEC-92A2-DFBB6B85624B}"/>
   </bookViews>
@@ -166,7 +166,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,6 +183,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -306,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -335,6 +343,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -649,10 +658,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{014F5967-FF16-4A7A-8914-B6A3D6DBE291}">
-  <dimension ref="A3:AJ13"/>
+  <dimension ref="A3:AJ34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="13.44140625" customWidth="1"/>
     <col min="4" max="4" width="13.88671875" customWidth="1"/>
@@ -975,8 +984,12 @@
         <v>0</v>
       </c>
     </row>
+    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I34" s="14"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Diagrama de Gantt.xlsx
+++ b/Diagrama de Gantt.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\df335\Desktop\ProyectoFinDeCursoGrupo5\ProyectoFinDeCursoGrupo5\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C39ABC0-21FE-46E5-B23C-9CFFA7B61D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -22,12 +28,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>27 de Marzo</t>
   </si>
@@ -138,9 +147,6 @@
   </si>
   <si>
     <t>IDEAR</t>
-  </si>
-  <si>
-    <t>ENTREGA</t>
   </si>
   <si>
     <t>EXPLORAR</t>
@@ -158,14 +164,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* \-??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,159 +188,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,198 +210,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149998474074526"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="0" tint="-0.14996795556505021"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -640,251 +303,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -917,61 +338,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Coma" xfId="1" builtinId="3"/>
-    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
-    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
-    <cellStyle name="Coma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Moneda [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hipervínculo" xfId="6" builtinId="8"/>
-    <cellStyle name="Hipervínculo visitado" xfId="7" builtinId="9"/>
-    <cellStyle name="Nota" xfId="8" builtinId="10"/>
-    <cellStyle name="Texto de advertencia" xfId="9" builtinId="11"/>
-    <cellStyle name="Título" xfId="10" builtinId="15"/>
-    <cellStyle name="Texto explicativo" xfId="11" builtinId="53"/>
-    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
-    <cellStyle name="Salida" xfId="17" builtinId="21"/>
-    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
-    <cellStyle name="Celda de comprobación" xfId="19" builtinId="23"/>
-    <cellStyle name="Celda vinculada" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Correcto" xfId="22" builtinId="26"/>
-    <cellStyle name="Incorrecto" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
-    <cellStyle name="Énfasis1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Énfasis1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Énfasis1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Énfasis1" xfId="28" builtinId="32"/>
-    <cellStyle name="Énfasis2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Énfasis2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Énfasis2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Énfasis2" xfId="32" builtinId="36"/>
-    <cellStyle name="Énfasis3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Énfasis3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Énfasis3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Énfasis3" xfId="36" builtinId="40"/>
-    <cellStyle name="Énfasis4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Énfasis4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Énfasis4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Énfasis4" xfId="40" builtinId="44"/>
-    <cellStyle name="Énfasis5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Énfasis5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Énfasis5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Énfasis5" xfId="44" builtinId="48"/>
-    <cellStyle name="Énfasis6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Énfasis6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Énfasis6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Énfasis6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1229,25 +606,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A3:AJ34"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A4:AJ34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="13.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="13.4444444444444" customWidth="1"/>
-    <col min="4" max="4" width="13.8888888888889" customWidth="1"/>
-    <col min="5" max="5" width="13.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15.15"/>
-    <row r="4" s="1" customFormat="1" ht="19.2" customHeight="1" spans="1:36">
+    <row r="4" spans="1:36" s="1" customFormat="1" ht="19.2" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="3" t="s">
         <v>0</v>
@@ -1355,7 +731,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" ht="28.2" customHeight="1" spans="1:36">
+    <row r="5" spans="1:36" ht="28.2" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>35</v>
       </c>
@@ -1395,7 +771,7 @@
       <c r="AI5" s="7"/>
       <c r="AJ5" s="12"/>
     </row>
-    <row r="6" ht="28.2" customHeight="1" spans="1:36">
+    <row r="6" spans="1:36" ht="28.2" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>36</v>
       </c>
@@ -1413,9 +789,7 @@
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
-      <c r="P6" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="P6" s="6"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
@@ -1437,9 +811,9 @@
       <c r="AI6" s="7"/>
       <c r="AJ6" s="12"/>
     </row>
-    <row r="7" ht="28.2" customHeight="1" spans="1:36">
+    <row r="7" spans="1:36" ht="28.2" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1477,9 +851,9 @@
       <c r="AI7" s="7"/>
       <c r="AJ7" s="12"/>
     </row>
-    <row r="8" ht="28.2" customHeight="1" spans="1:36">
+    <row r="8" spans="1:36" ht="28.2" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1517,9 +891,9 @@
       <c r="AI8" s="7"/>
       <c r="AJ8" s="12"/>
     </row>
-    <row r="9" ht="28.2" customHeight="1" spans="1:36">
+    <row r="9" spans="1:36" ht="28.2" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -1557,10 +931,9 @@
       <c r="AI9" s="13"/>
       <c r="AJ9" s="14"/>
     </row>
-    <row r="10" ht="15.15"/>
-    <row r="13" spans="7:7">
+    <row r="13" spans="1:36">
       <c r="G13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="9:9">
@@ -1569,6 +942,5 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>